--- a/src/analyses/linear_regression/all_anova_passed_cells.xlsx
+++ b/src/analyses/linear_regression/all_anova_passed_cells.xlsx
@@ -17,8 +17,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -429,2016 +429,2674 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G76"/>
+  <dimension ref="A1:I76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Unnamed: 0</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Round No.</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Round No.</t>
+          <t>Time Window</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Time Window</t>
+          <t>Channel</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Cell</t>
+          <t>P Value</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>P Value</t>
+          <t>NeuronID</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WindowStart_ms</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>WindowEnd_ms</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>51</v>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="n">
         <v>45195</v>
       </c>
-      <c r="D2" t="n">
+      <c r="C2" t="n">
         <v>1</v>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>(0.0, 300.0)</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>(0.0, 300.0)</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
           <t>Channel.C_027_Unit 1</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="F2" t="n">
         <v>0.030965715390678</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2023-09-26_1_Channel.C_027_Unit 1</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>300</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="B3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="n">
         <v>45195</v>
       </c>
-      <c r="D3" t="n">
+      <c r="C3" t="n">
         <v>2</v>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>(700.0, 1000.0)</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>(700.0, 1000.0)</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
           <t>Channel.C_011_Unit 1</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="F3" t="n">
         <v>0.0224122204061938</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2023-09-26_2_Channel.C_011_Unit 1</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>700</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="2" t="n">
         <v>45195</v>
       </c>
-      <c r="D4" t="n">
+      <c r="C4" t="n">
         <v>2</v>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>(50.0, 150.0)</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>(50.0, 150.0)</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
           <t>Channel.C_020</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="F4" t="n">
         <v>0.00488467703525351</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2023-09-26_2_Channel.C_020</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>50</v>
+      </c>
+      <c r="I4" t="n">
+        <v>150</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>52</v>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="2" t="n">
         <v>45195</v>
       </c>
-      <c r="D5" t="n">
+      <c r="C5" t="n">
         <v>3</v>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>(0.0, 2000.0)</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>(0.0, 2000.0)</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
           <t>Channel.C_002_Unit 1</t>
         </is>
       </c>
-      <c r="G5" t="n">
+      <c r="F5" t="n">
         <v>0.0001048561426</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2023-09-26_3_Channel.C_002_Unit 1</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2000</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" t="n">
-        <v>2</v>
-      </c>
-      <c r="C6" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="2" t="n">
         <v>45195</v>
       </c>
-      <c r="D6" t="n">
+      <c r="C6" t="n">
         <v>3</v>
       </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>(100.0, 200.0)</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>(100.0, 200.0)</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
           <t>Channel.C_007_Unit 2</t>
         </is>
       </c>
-      <c r="G6" t="n">
+      <c r="F6" t="n">
         <v>0.031938468862498</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2023-09-26_3_Channel.C_007_Unit 2</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>100</v>
+      </c>
+      <c r="I6" t="n">
+        <v>200</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45195</v>
+      </c>
+      <c r="C7" t="n">
         <v>3</v>
       </c>
-      <c r="B7" t="n">
-        <v>3</v>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>45195</v>
-      </c>
-      <c r="D7" t="n">
-        <v>3</v>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>(150.0, 350.0)</t>
+        </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>(150.0, 350.0)</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
           <t>Channel.C_027_Unit 2</t>
         </is>
       </c>
-      <c r="G7" t="n">
+      <c r="F7" t="n">
         <v>0.0459134288678394</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2023-09-26_3_Channel.C_027_Unit 2</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>150</v>
+      </c>
+      <c r="I7" t="n">
+        <v>350</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="B8" t="n">
-        <v>4</v>
-      </c>
-      <c r="C8" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="2" t="n">
         <v>45202</v>
       </c>
-      <c r="D8" t="n">
+      <c r="C8" t="n">
         <v>3</v>
       </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>(200.0, 400.0)</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>(200.0, 400.0)</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
           <t>Channel.C_006_Unit 1</t>
         </is>
       </c>
-      <c r="G8" t="n">
+      <c r="F8" t="n">
         <v>0.000205299212230494</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2023-10-03_3_Channel.C_006_Unit 1</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>200</v>
+      </c>
+      <c r="I8" t="n">
+        <v>400</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="B9" t="n">
-        <v>5</v>
-      </c>
-      <c r="C9" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="2" t="n">
         <v>45202</v>
       </c>
-      <c r="D9" t="n">
+      <c r="C9" t="n">
         <v>3</v>
       </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>(2150.0, 2250.0)</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>(2150.0, 2250.0)</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
           <t>Channel.C_006_Unit 1</t>
         </is>
       </c>
-      <c r="G9" t="n">
+      <c r="F9" t="n">
         <v>0.000219903122149023</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2023-10-03_3_Channel.C_006_Unit 1</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>2150</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2250</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>53</v>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="2" t="n">
         <v>45202</v>
       </c>
-      <c r="D10" t="n">
+      <c r="C10" t="n">
         <v>3</v>
       </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>(200.0, 600.0)</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>(200.0, 600.0)</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
           <t>Channel.C_013_Unit 1</t>
         </is>
       </c>
-      <c r="G10" t="n">
+      <c r="F10" t="n">
         <v>0.03527854547184</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2023-10-03_3_Channel.C_013_Unit 1</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>200</v>
+      </c>
+      <c r="I10" t="n">
+        <v>600</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="B11" t="n">
-        <v>6</v>
-      </c>
-      <c r="C11" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="2" t="n">
         <v>45202</v>
       </c>
-      <c r="D11" t="n">
+      <c r="C11" t="n">
         <v>3</v>
       </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>(1900.0, 2000.0)</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>(1900.0, 2000.0)</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
           <t>Channel.C_026_Unit 1</t>
         </is>
       </c>
-      <c r="G11" t="n">
+      <c r="F11" t="n">
         <v>0.00127725376352979</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2023-10-03_3_Channel.C_026_Unit 1</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>1900</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2000</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="B12" t="n">
-        <v>7</v>
-      </c>
-      <c r="C12" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="2" t="n">
         <v>45202</v>
       </c>
-      <c r="D12" t="n">
+      <c r="C12" t="n">
         <v>4</v>
       </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>(450.0, 650.0)</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>(450.0, 650.0)</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
           <t>Channel.C_006</t>
         </is>
       </c>
-      <c r="G12" t="n">
+      <c r="F12" t="n">
         <v>0.00707558272740489</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2023-10-03_4_Channel.C_006</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>450</v>
+      </c>
+      <c r="I12" t="n">
+        <v>650</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="B13" t="n">
-        <v>8</v>
-      </c>
-      <c r="C13" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" s="2" t="n">
         <v>45202</v>
       </c>
-      <c r="D13" t="n">
+      <c r="C13" t="n">
         <v>4</v>
       </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>(200.0, 650.0)</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>(200.0, 650.0)</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
           <t>Channel.C_010_Unit 2</t>
         </is>
       </c>
-      <c r="G13" t="n">
+      <c r="F13" t="n">
         <v>0.00159172655600108</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2023-10-03_4_Channel.C_010_Unit 2</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>200</v>
+      </c>
+      <c r="I13" t="n">
+        <v>650</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>54</v>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" s="2" t="n">
         <v>45202</v>
       </c>
-      <c r="D14" t="n">
+      <c r="C14" t="n">
         <v>4</v>
       </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>(200.0, 600.0)</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>(200.0, 600.0)</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
           <t>Channel.C_010_Unit 2</t>
         </is>
       </c>
-      <c r="G14" t="n">
+      <c r="F14" t="n">
         <v>0.000378311542831</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2023-10-03_4_Channel.C_010_Unit 2</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>200</v>
+      </c>
+      <c r="I14" t="n">
+        <v>600</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="B15" t="n">
-        <v>9</v>
-      </c>
-      <c r="C15" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" s="2" t="n">
         <v>45202</v>
       </c>
-      <c r="D15" t="n">
+      <c r="C15" t="n">
         <v>4</v>
       </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>(1000.0, 1100.0)</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>(1000.0, 1100.0)</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
           <t>Channel.C_026</t>
         </is>
       </c>
-      <c r="G15" t="n">
+      <c r="F15" t="n">
         <v>0.0470807977888419</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2023-10-03_4_Channel.C_026</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1100</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="B16" t="n">
-        <v>10</v>
-      </c>
-      <c r="C16" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" s="2" t="n">
         <v>45203</v>
       </c>
-      <c r="D16" t="n">
+      <c r="C16" t="n">
         <v>1</v>
       </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>(150.0, 400.0)</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>(150.0, 400.0)</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
           <t>Channel.C_004_Unit 1</t>
         </is>
       </c>
-      <c r="G16" t="n">
+      <c r="F16" t="n">
         <v>7.5061489843254e-07</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2023-10-04_1_Channel.C_004_Unit 1</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>150</v>
+      </c>
+      <c r="I16" t="n">
+        <v>400</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>55</v>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" s="2" t="n">
         <v>45203</v>
       </c>
-      <c r="D17" t="n">
+      <c r="C17" t="n">
         <v>1</v>
       </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>(100.0, 700.0)</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>(100.0, 700.0)</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
           <t>Channel.C_004_Unit 1</t>
         </is>
       </c>
-      <c r="G17" t="n">
+      <c r="F17" t="n">
         <v>1.05830081034659e-06</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2023-10-04_1_Channel.C_004_Unit 1</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>100</v>
+      </c>
+      <c r="I17" t="n">
+        <v>700</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="B18" t="n">
-        <v>11</v>
-      </c>
-      <c r="C18" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" s="2" t="n">
         <v>45203</v>
       </c>
-      <c r="D18" t="n">
+      <c r="C18" t="n">
         <v>1</v>
       </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>(150.0, 400.0)</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>(150.0, 400.0)</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
           <t>Channel.C_019_Unit 3</t>
         </is>
       </c>
-      <c r="G18" t="n">
+      <c r="F18" t="n">
         <v>5.0489588623909e-05</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2023-10-04_1_Channel.C_019_Unit 3</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>150</v>
+      </c>
+      <c r="I18" t="n">
+        <v>400</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>56</v>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" s="2" t="n">
         <v>45203</v>
       </c>
-      <c r="D19" t="n">
+      <c r="C19" t="n">
         <v>1</v>
       </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>(100.0, 500.0)</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>(100.0, 500.0)</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
           <t>Channel.C_019_Unit 3</t>
         </is>
       </c>
-      <c r="G19" t="n">
+      <c r="F19" t="n">
         <v>2.13976612550698e-05</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2023-10-04_1_Channel.C_019_Unit 3</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>100</v>
+      </c>
+      <c r="I19" t="n">
+        <v>500</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="B20" t="n">
-        <v>12</v>
-      </c>
-      <c r="C20" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" s="2" t="n">
         <v>45203</v>
       </c>
-      <c r="D20" t="n">
+      <c r="C20" t="n">
         <v>2</v>
       </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>(150.0, 500.0)</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>(150.0, 500.0)</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
           <t>Channel.C_018_Unit 1</t>
         </is>
       </c>
-      <c r="G20" t="n">
+      <c r="F20" t="n">
         <v>1.51626385288723e-11</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2023-10-04_2_Channel.C_018_Unit 1</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>150</v>
+      </c>
+      <c r="I20" t="n">
+        <v>500</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>57</v>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" s="2" t="n">
         <v>45203</v>
       </c>
-      <c r="D21" t="n">
+      <c r="C21" t="n">
         <v>2</v>
       </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>(100.0, 500.0)</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>(100.0, 500.0)</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
           <t>Channel.C_018_Unit 1</t>
         </is>
       </c>
-      <c r="G21" t="n">
+      <c r="F21" t="n">
         <v>7.55699317281293e-11</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2023-10-04_2_Channel.C_018_Unit 1</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>100</v>
+      </c>
+      <c r="I21" t="n">
+        <v>500</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>58</v>
-      </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" s="2" t="n">
         <v>45203</v>
       </c>
-      <c r="D22" t="n">
+      <c r="C22" t="n">
         <v>2</v>
       </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>(0.0, 2000.0)</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>(0.0, 2000.0)</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
           <t>Channel.C_020_Unit 2</t>
         </is>
       </c>
-      <c r="G22" t="n">
+      <c r="F22" t="n">
         <v>1.66280772505988e-05</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>2023-10-04_2_Channel.C_020_Unit 2</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2000</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="B23" t="n">
-        <v>13</v>
-      </c>
-      <c r="C23" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" s="2" t="n">
         <v>45203</v>
       </c>
-      <c r="D23" t="n">
+      <c r="C23" t="n">
         <v>3</v>
       </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>(150.0, 400.0)</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>(150.0, 400.0)</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
           <t>Channel.C_002_Unit 1</t>
         </is>
       </c>
-      <c r="G23" t="n">
+      <c r="F23" t="n">
         <v>4.82855775313535e-05</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2023-10-04_3_Channel.C_002_Unit 1</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>150</v>
+      </c>
+      <c r="I23" t="n">
+        <v>400</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>59</v>
-      </c>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" s="2" t="n">
         <v>45203</v>
       </c>
-      <c r="D24" t="n">
+      <c r="C24" t="n">
         <v>3</v>
       </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>(0.0, 500.0)</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>(0.0, 500.0)</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
           <t>Channel.C_002_Unit 1</t>
         </is>
       </c>
-      <c r="G24" t="n">
+      <c r="F24" t="n">
         <v>2.33114874428906e-05</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2023-10-04_3_Channel.C_002_Unit 1</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>500</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="B25" t="n">
-        <v>14</v>
-      </c>
-      <c r="C25" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" s="2" t="n">
         <v>45203</v>
       </c>
-      <c r="D25" t="n">
+      <c r="C25" t="n">
         <v>3</v>
       </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>(100.0, 500.0)</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>(100.0, 500.0)</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
           <t>Channel.C_004_Unit 2</t>
         </is>
       </c>
-      <c r="G25" t="n">
+      <c r="F25" t="n">
         <v>0.0353088450142687</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2023-10-04_3_Channel.C_004_Unit 2</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>100</v>
+      </c>
+      <c r="I25" t="n">
+        <v>500</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>60</v>
-      </c>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" s="2" t="n">
         <v>45203</v>
       </c>
-      <c r="D26" t="n">
+      <c r="C26" t="n">
         <v>3</v>
       </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>(0.0, 500.0)</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>(0.0, 500.0)</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
           <t>Channel.C_004_Unit 2</t>
         </is>
       </c>
-      <c r="G26" t="n">
+      <c r="F26" t="n">
         <v>0.012545428798116</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2023-10-04_3_Channel.C_004_Unit 2</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>500</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="B27" t="n">
-        <v>15</v>
-      </c>
-      <c r="C27" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" s="2" t="n">
         <v>45203</v>
       </c>
-      <c r="D27" t="n">
+      <c r="C27" t="n">
         <v>3</v>
       </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>(150.0, 500.0)</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>(150.0, 500.0)</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
           <t>Channel.C_009_Unit 1</t>
         </is>
       </c>
-      <c r="G27" t="n">
+      <c r="F27" t="n">
         <v>0.00104884300249579</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2023-10-04_3_Channel.C_009_Unit 1</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>150</v>
+      </c>
+      <c r="I27" t="n">
+        <v>500</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>61</v>
-      </c>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" s="2" t="n">
         <v>45203</v>
       </c>
-      <c r="D28" t="n">
+      <c r="C28" t="n">
         <v>3</v>
       </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>(0.0, 2000.0)</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>(0.0, 2000.0)</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
           <t>Channel.C_009_Unit 1</t>
         </is>
       </c>
-      <c r="G28" t="n">
+      <c r="F28" t="n">
         <v>0.038781460115805</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2023-10-04_3_Channel.C_009_Unit 1</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>2000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="B29" t="n">
-        <v>16</v>
-      </c>
-      <c r="C29" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" s="2" t="n">
         <v>45203</v>
       </c>
-      <c r="D29" t="n">
+      <c r="C29" t="n">
         <v>3</v>
       </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>(100.0, 450.0)</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>(100.0, 450.0)</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
           <t>Channel.C_009_Unit 3</t>
         </is>
       </c>
-      <c r="G29" t="n">
+      <c r="F29" t="n">
         <v>0.0395639912055182</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2023-10-04_3_Channel.C_009_Unit 3</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>100</v>
+      </c>
+      <c r="I29" t="n">
+        <v>450</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>62</v>
-      </c>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" s="2" t="n">
         <v>45203</v>
       </c>
-      <c r="D30" t="n">
+      <c r="C30" t="n">
         <v>3</v>
       </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>(0.0, 700.0)</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>(0.0, 700.0)</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
           <t>Channel.C_009_Unit 3</t>
         </is>
       </c>
-      <c r="G30" t="n">
+      <c r="F30" t="n">
         <v>0.042377881281726</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2023-10-04_3_Channel.C_009_Unit 3</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>700</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="B31" t="n">
-        <v>17</v>
-      </c>
-      <c r="C31" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" s="2" t="n">
         <v>45203</v>
       </c>
-      <c r="D31" t="n">
+      <c r="C31" t="n">
         <v>4</v>
       </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>(150.0, 450.0)</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>(150.0, 450.0)</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
           <t>Channel.C_021_Unit 2</t>
         </is>
       </c>
-      <c r="G31" t="n">
+      <c r="F31" t="n">
         <v>0.0410304872185249</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2023-10-04_4_Channel.C_021_Unit 2</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>150</v>
+      </c>
+      <c r="I31" t="n">
+        <v>450</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="B32" t="n">
-        <v>18</v>
-      </c>
-      <c r="C32" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" s="2" t="n">
         <v>45203</v>
       </c>
-      <c r="D32" t="n">
+      <c r="C32" t="n">
         <v>4</v>
       </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>(150.0, 650.0)</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>(150.0, 650.0)</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
           <t>Channel.C_022_Unit 2</t>
         </is>
       </c>
-      <c r="G32" t="n">
+      <c r="F32" t="n">
         <v>0.00168825852991398</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>2023-10-04_4_Channel.C_022_Unit 2</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>150</v>
+      </c>
+      <c r="I32" t="n">
+        <v>650</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>63</v>
-      </c>
-      <c r="B33" t="inlineStr"/>
-      <c r="C33" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" s="2" t="n">
         <v>45203</v>
       </c>
-      <c r="D33" t="n">
+      <c r="C33" t="n">
         <v>4</v>
       </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>(0.0, 750.0)</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>(0.0, 750.0)</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
           <t>Channel.C_022_Unit 2</t>
         </is>
       </c>
-      <c r="G33" t="n">
+      <c r="F33" t="n">
         <v>0.011944886356068</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2023-10-04_4_Channel.C_022_Unit 2</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>750</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="B34" t="n">
-        <v>19</v>
-      </c>
-      <c r="C34" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" s="2" t="n">
         <v>45203</v>
       </c>
-      <c r="D34" t="n">
+      <c r="C34" t="n">
         <v>4</v>
       </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>(350.0, 650.0)</t>
+        </is>
+      </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>(350.0, 650.0)</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
           <t>Channel.C_027_Unit 1</t>
         </is>
       </c>
-      <c r="G34" t="n">
+      <c r="F34" t="n">
         <v>0.00016076355362287</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2023-10-04_4_Channel.C_027_Unit 1</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>350</v>
+      </c>
+      <c r="I34" t="n">
+        <v>650</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>64</v>
-      </c>
-      <c r="B35" t="inlineStr"/>
-      <c r="C35" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" s="2" t="n">
         <v>45203</v>
       </c>
-      <c r="D35" t="n">
+      <c r="C35" t="n">
         <v>4</v>
       </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>(250.0, 750.0)</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>(250.0, 750.0)</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
           <t>Channel.C_027_Unit 1</t>
         </is>
       </c>
-      <c r="G35" t="n">
+      <c r="F35" t="n">
         <v>0.00029232953002</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>2023-10-04_4_Channel.C_027_Unit 1</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>250</v>
+      </c>
+      <c r="I35" t="n">
+        <v>750</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>65</v>
-      </c>
-      <c r="B36" t="inlineStr"/>
-      <c r="C36" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" s="2" t="n">
         <v>45204</v>
       </c>
-      <c r="D36" t="n">
+      <c r="C36" t="n">
         <v>1</v>
       </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>(0.0, 2000.0)</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>(0.0, 2000.0)</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
           <t>Channel.C_004</t>
         </is>
       </c>
-      <c r="G36" t="n">
+      <c r="F36" t="n">
         <v>0.009867667579969999</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2023-10-05_1_Channel.C_004</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>2000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="B37" t="n">
-        <v>20</v>
-      </c>
-      <c r="C37" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" s="2" t="n">
         <v>45204</v>
       </c>
-      <c r="D37" t="n">
+      <c r="C37" t="n">
         <v>1</v>
       </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>(1000.0, 1100.0)</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>(1000.0, 1100.0)</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
           <t>Channel.C_004_Unit 1</t>
         </is>
       </c>
-      <c r="G37" t="n">
+      <c r="F37" t="n">
         <v>0.0451555088063392</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2023-10-05_1_Channel.C_004_Unit 1</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1100</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="B38" t="n">
-        <v>21</v>
-      </c>
-      <c r="C38" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" s="2" t="n">
         <v>45204</v>
       </c>
-      <c r="D38" t="n">
+      <c r="C38" t="n">
         <v>2</v>
       </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>(500.0, 850.0)</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>(500.0, 850.0)</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
           <t>Channel.C_009_Unit 1</t>
         </is>
       </c>
-      <c r="G38" t="n">
+      <c r="F38" t="n">
         <v>0.000937658799145095</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2023-10-05_2_Channel.C_009_Unit 1</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
+        <v>500</v>
+      </c>
+      <c r="I38" t="n">
+        <v>850</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="B39" t="n">
-        <v>22</v>
-      </c>
-      <c r="C39" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" s="2" t="n">
         <v>45204</v>
       </c>
-      <c r="D39" t="n">
+      <c r="C39" t="n">
         <v>2</v>
       </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>(50.0, 350.0)</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>(50.0, 350.0)</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
           <t>Channel.C_018_Unit 1</t>
         </is>
       </c>
-      <c r="G39" t="n">
+      <c r="F39" t="n">
         <v>0.0146381959778083</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2023-10-05_2_Channel.C_018_Unit 1</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>50</v>
+      </c>
+      <c r="I39" t="n">
+        <v>350</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="B40" t="n">
-        <v>23</v>
-      </c>
-      <c r="C40" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" s="2" t="n">
         <v>45204</v>
       </c>
-      <c r="D40" t="n">
+      <c r="C40" t="n">
         <v>2</v>
       </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>(2200.0, 2300.0)</t>
+        </is>
+      </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>(2200.0, 2300.0)</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
           <t>Channel.C_019_Unit 2</t>
         </is>
       </c>
-      <c r="G40" t="n">
+      <c r="F40" t="n">
         <v>0.0416051516577862</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2023-10-05_2_Channel.C_019_Unit 2</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>2200</v>
+      </c>
+      <c r="I40" t="n">
+        <v>2300</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="B41" t="n">
-        <v>24</v>
-      </c>
-      <c r="C41" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" s="2" t="n">
         <v>45208</v>
       </c>
-      <c r="D41" t="n">
+      <c r="C41" t="n">
         <v>3</v>
       </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>(600.0, 750.0)</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>(600.0, 750.0)</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
           <t>Channel.C_013</t>
         </is>
       </c>
-      <c r="G41" t="n">
+      <c r="F41" t="n">
         <v>0.0179426294938499</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2023-10-09_3_Channel.C_013</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>600</v>
+      </c>
+      <c r="I41" t="n">
+        <v>750</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="B42" t="n">
-        <v>25</v>
-      </c>
-      <c r="C42" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" s="2" t="n">
         <v>45209</v>
       </c>
-      <c r="D42" t="n">
+      <c r="C42" t="n">
         <v>2</v>
       </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>(1150.0, 1250.0)</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>(1150.0, 1250.0)</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
           <t>Channel.C_007</t>
         </is>
       </c>
-      <c r="G42" t="n">
+      <c r="F42" t="n">
         <v>0.0299065586144327</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2023-10-10_2_Channel.C_007</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>1150</v>
+      </c>
+      <c r="I42" t="n">
+        <v>1250</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="B43" t="n">
-        <v>26</v>
-      </c>
-      <c r="C43" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="B43" s="2" t="n">
         <v>45209</v>
       </c>
-      <c r="D43" t="n">
+      <c r="C43" t="n">
         <v>2</v>
       </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>(400.0, 600.0)</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>(400.0, 600.0)</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
           <t>Channel.C_011</t>
         </is>
       </c>
-      <c r="G43" t="n">
+      <c r="F43" t="n">
         <v>0.0207972809620275</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2023-10-10_2_Channel.C_011</t>
+        </is>
+      </c>
+      <c r="H43" t="n">
+        <v>400</v>
+      </c>
+      <c r="I43" t="n">
+        <v>600</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>27</v>
-      </c>
-      <c r="B44" t="n">
-        <v>27</v>
-      </c>
-      <c r="C44" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="B44" s="2" t="n">
         <v>45209</v>
       </c>
-      <c r="D44" t="n">
+      <c r="C44" t="n">
         <v>2</v>
       </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>(300.0, 550.0)</t>
+        </is>
+      </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>(300.0, 550.0)</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
           <t>Channel.C_021</t>
         </is>
       </c>
-      <c r="G44" t="n">
+      <c r="F44" t="n">
         <v>0.0109178027087272</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2023-10-10_2_Channel.C_021</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>300</v>
+      </c>
+      <c r="I44" t="n">
+        <v>550</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>28</v>
-      </c>
-      <c r="B45" t="n">
-        <v>28</v>
-      </c>
-      <c r="C45" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="B45" s="2" t="n">
         <v>45209</v>
       </c>
-      <c r="D45" t="n">
+      <c r="C45" t="n">
         <v>2</v>
       </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>(1550.0, 1650.0)</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>(1550.0, 1650.0)</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
           <t>Channel.C_021</t>
         </is>
       </c>
-      <c r="G45" t="n">
+      <c r="F45" t="n">
         <v>0.0421362181422794</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2023-10-10_2_Channel.C_021</t>
+        </is>
+      </c>
+      <c r="H45" t="n">
+        <v>1550</v>
+      </c>
+      <c r="I45" t="n">
+        <v>1650</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>29</v>
-      </c>
-      <c r="B46" t="n">
-        <v>29</v>
-      </c>
-      <c r="C46" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="B46" s="2" t="n">
         <v>45210</v>
       </c>
-      <c r="D46" t="n">
+      <c r="C46" t="n">
         <v>1</v>
       </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>(150.0, 400.0)</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>(150.0, 400.0)</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
           <t>Channel.C_002</t>
         </is>
       </c>
-      <c r="G46" t="n">
+      <c r="F46" t="n">
         <v>3.38332280973613e-05</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2023-10-11_1_Channel.C_002</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
+        <v>150</v>
+      </c>
+      <c r="I46" t="n">
+        <v>400</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>66</v>
-      </c>
-      <c r="B47" t="inlineStr"/>
-      <c r="C47" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="B47" s="2" t="n">
         <v>45210</v>
       </c>
-      <c r="D47" t="n">
+      <c r="C47" t="n">
         <v>1</v>
       </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>(100.0, 500.0)</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>(100.0, 500.0)</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
           <t>Channel.C_002</t>
         </is>
       </c>
-      <c r="G47" t="n">
+      <c r="F47" t="n">
         <v>1.49682454822413e-05</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2023-10-11_1_Channel.C_002</t>
+        </is>
+      </c>
+      <c r="H47" t="n">
+        <v>100</v>
+      </c>
+      <c r="I47" t="n">
+        <v>500</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>30</v>
-      </c>
-      <c r="B48" t="n">
-        <v>30</v>
-      </c>
-      <c r="C48" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="B48" s="2" t="n">
         <v>45210</v>
       </c>
-      <c r="D48" t="n">
+      <c r="C48" t="n">
         <v>1</v>
       </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>(2000.0, 2200.0)</t>
+        </is>
+      </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>(2000.0, 2200.0)</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
           <t>Channel.C_010</t>
         </is>
       </c>
-      <c r="G48" t="n">
+      <c r="F48" t="n">
         <v>0.0416891737433396</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2023-10-11_1_Channel.C_010</t>
+        </is>
+      </c>
+      <c r="H48" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I48" t="n">
+        <v>2200</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>67</v>
-      </c>
-      <c r="B49" t="inlineStr"/>
-      <c r="C49" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="B49" s="2" t="n">
         <v>45210</v>
       </c>
-      <c r="D49" t="n">
+      <c r="C49" t="n">
         <v>3</v>
       </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>(0.0, 2000.0)</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>(0.0, 2000.0)</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
           <t>Channel.C_002</t>
         </is>
       </c>
-      <c r="G49" t="n">
+      <c r="F49" t="n">
         <v>0.009555414268795999</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>2023-10-11_3_Channel.C_002</t>
+        </is>
+      </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" t="n">
+        <v>2000</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>31</v>
-      </c>
-      <c r="B50" t="n">
-        <v>31</v>
-      </c>
-      <c r="C50" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B50" s="2" t="n">
         <v>45210</v>
       </c>
-      <c r="D50" t="n">
+      <c r="C50" t="n">
         <v>3</v>
       </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>(1650.0, 1800.0)</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>(1650.0, 1800.0)</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
           <t>Channel.C_013</t>
         </is>
       </c>
-      <c r="G50" t="n">
+      <c r="F50" t="n">
         <v>0.00580553000234327</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>2023-10-11_3_Channel.C_013</t>
+        </is>
+      </c>
+      <c r="H50" t="n">
+        <v>1650</v>
+      </c>
+      <c r="I50" t="n">
+        <v>1800</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>68</v>
-      </c>
-      <c r="B51" t="inlineStr"/>
-      <c r="C51" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="B51" s="2" t="n">
         <v>45210</v>
       </c>
-      <c r="D51" t="n">
+      <c r="C51" t="n">
         <v>3</v>
       </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>(0.0, 2000.0)</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>(0.0, 2000.0)</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
           <t>Channel.C_013</t>
         </is>
       </c>
-      <c r="G51" t="n">
+      <c r="F51" t="n">
         <v>0.001540377255957</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>2023-10-11_3_Channel.C_013</t>
+        </is>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" t="n">
+        <v>2000</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>69</v>
-      </c>
-      <c r="B52" t="inlineStr"/>
-      <c r="C52" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="B52" s="2" t="n">
         <v>45223</v>
       </c>
-      <c r="D52" t="n">
+      <c r="C52" t="n">
         <v>2</v>
       </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>(250.0, 750.0)</t>
+        </is>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>(250.0, 750.0)</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
           <t>Channel.C_002</t>
         </is>
       </c>
-      <c r="G52" t="n">
+      <c r="F52" t="n">
         <v>0.01126620279013</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>2023-10-24_2_Channel.C_002</t>
+        </is>
+      </c>
+      <c r="H52" t="n">
+        <v>250</v>
+      </c>
+      <c r="I52" t="n">
+        <v>750</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>32</v>
-      </c>
-      <c r="B53" t="n">
-        <v>32</v>
-      </c>
-      <c r="C53" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="B53" s="2" t="n">
         <v>45226</v>
       </c>
-      <c r="D53" t="n">
+      <c r="C53" t="n">
         <v>3</v>
       </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>(1750.0, 1900.0)</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>(1750.0, 1900.0)</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
           <t>Channel.C_007</t>
         </is>
       </c>
-      <c r="G53" t="n">
+      <c r="F53" t="n">
         <v>0.0163236212793226</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2023-10-27_3_Channel.C_007</t>
+        </is>
+      </c>
+      <c r="H53" t="n">
+        <v>1750</v>
+      </c>
+      <c r="I53" t="n">
+        <v>1900</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>33</v>
-      </c>
-      <c r="B54" t="n">
-        <v>33</v>
-      </c>
-      <c r="C54" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="B54" s="2" t="n">
         <v>45226</v>
       </c>
-      <c r="D54" t="n">
+      <c r="C54" t="n">
         <v>3</v>
       </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>(1600.0, 1900.0)</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>(1600.0, 1900.0)</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
           <t>Channel.C_013</t>
         </is>
       </c>
-      <c r="G54" t="n">
+      <c r="F54" t="n">
         <v>0.0494787080515314</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>2023-10-27_3_Channel.C_013</t>
+        </is>
+      </c>
+      <c r="H54" t="n">
+        <v>1600</v>
+      </c>
+      <c r="I54" t="n">
+        <v>1900</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>34</v>
-      </c>
-      <c r="B55" t="n">
-        <v>34</v>
-      </c>
-      <c r="C55" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="B55" s="2" t="n">
         <v>45226</v>
       </c>
-      <c r="D55" t="n">
+      <c r="C55" t="n">
         <v>4</v>
       </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>(200.0, 700.0)</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>(200.0, 700.0)</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
           <t>Channel.C_011</t>
         </is>
       </c>
-      <c r="G55" t="n">
+      <c r="F55" t="n">
         <v>0.00665026125701438</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>2023-10-27_4_Channel.C_011</t>
+        </is>
+      </c>
+      <c r="H55" t="n">
+        <v>200</v>
+      </c>
+      <c r="I55" t="n">
+        <v>700</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>70</v>
-      </c>
-      <c r="B56" t="inlineStr"/>
-      <c r="C56" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="B56" s="2" t="n">
         <v>45226</v>
       </c>
-      <c r="D56" t="n">
+      <c r="C56" t="n">
         <v>4</v>
       </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>(0.0, 750.0)</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>(0.0, 750.0)</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
           <t>Channel.C_011</t>
         </is>
       </c>
-      <c r="G56" t="n">
+      <c r="F56" t="n">
         <v>0.006289624603342</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>2023-10-27_4_Channel.C_011</t>
+        </is>
+      </c>
+      <c r="H56" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" t="n">
+        <v>750</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>35</v>
-      </c>
-      <c r="B57" t="n">
-        <v>35</v>
-      </c>
-      <c r="C57" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="B57" s="2" t="n">
         <v>45226</v>
       </c>
-      <c r="D57" t="n">
+      <c r="C57" t="n">
         <v>4</v>
       </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>(200.0, 650.0)</t>
+        </is>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>(200.0, 650.0)</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
           <t>Channel.C_020</t>
         </is>
       </c>
-      <c r="G57" t="n">
+      <c r="F57" t="n">
         <v>0.00763427299537475</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>2023-10-27_4_Channel.C_020</t>
+        </is>
+      </c>
+      <c r="H57" t="n">
+        <v>200</v>
+      </c>
+      <c r="I57" t="n">
+        <v>650</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>71</v>
-      </c>
-      <c r="B58" t="inlineStr"/>
-      <c r="C58" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="B58" s="2" t="n">
         <v>45226</v>
       </c>
-      <c r="D58" t="n">
+      <c r="C58" t="n">
         <v>4</v>
       </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>(0.0, 750.0)</t>
+        </is>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>(0.0, 750.0)</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
           <t>Channel.C_020</t>
         </is>
       </c>
-      <c r="G58" t="n">
+      <c r="F58" t="n">
         <v>0.006514719781525</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>2023-10-27_4_Channel.C_020</t>
+        </is>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" t="n">
+        <v>750</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>72</v>
-      </c>
-      <c r="B59" t="inlineStr"/>
-      <c r="C59" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="B59" s="2" t="n">
         <v>45230</v>
       </c>
-      <c r="D59" t="n">
+      <c r="C59" t="n">
         <v>1</v>
       </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>(250.0, 600.0)</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>(250.0, 600.0)</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
           <t>Channel.C_005</t>
         </is>
       </c>
-      <c r="G59" t="n">
+      <c r="F59" t="n">
         <v>0.004480491399968</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>2023-10-31_1_Channel.C_005</t>
+        </is>
+      </c>
+      <c r="H59" t="n">
+        <v>250</v>
+      </c>
+      <c r="I59" t="n">
+        <v>600</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>73</v>
-      </c>
-      <c r="B60" t="inlineStr"/>
-      <c r="C60" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="B60" s="2" t="n">
         <v>45230</v>
       </c>
-      <c r="D60" t="n">
+      <c r="C60" t="n">
         <v>1</v>
       </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>(100.0, 600.0)</t>
+        </is>
+      </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>(100.0, 600.0)</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
           <t>Channel.C_020</t>
         </is>
       </c>
-      <c r="G60" t="n">
+      <c r="F60" t="n">
         <v>0.011429781534636</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>2023-10-31_1_Channel.C_020</t>
+        </is>
+      </c>
+      <c r="H60" t="n">
+        <v>100</v>
+      </c>
+      <c r="I60" t="n">
+        <v>600</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>74</v>
-      </c>
-      <c r="B61" t="inlineStr"/>
-      <c r="C61" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="B61" s="2" t="n">
         <v>45238</v>
       </c>
-      <c r="D61" t="n">
+      <c r="C61" t="n">
         <v>1</v>
       </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>(100.0, 700.0)</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>(100.0, 700.0)</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
           <t>Channel.C_007</t>
         </is>
       </c>
-      <c r="G61" t="n">
+      <c r="F61" t="n">
         <v>0.000335148307695</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>2023-11-08_1_Channel.C_007</t>
+        </is>
+      </c>
+      <c r="H61" t="n">
+        <v>100</v>
+      </c>
+      <c r="I61" t="n">
+        <v>700</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>36</v>
-      </c>
-      <c r="B62" t="n">
-        <v>36</v>
-      </c>
-      <c r="C62" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="B62" s="2" t="n">
         <v>45250</v>
       </c>
-      <c r="D62" t="n">
+      <c r="C62" t="n">
         <v>1</v>
       </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>(850.0, 950.0)</t>
+        </is>
+      </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>(850.0, 950.0)</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
           <t>Channel.C_013</t>
         </is>
       </c>
-      <c r="G62" t="n">
+      <c r="F62" t="n">
         <v>0.0332634341315389</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>2023-11-20_1_Channel.C_013</t>
+        </is>
+      </c>
+      <c r="H62" t="n">
+        <v>850</v>
+      </c>
+      <c r="I62" t="n">
+        <v>950</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>37</v>
-      </c>
-      <c r="B63" t="n">
-        <v>37</v>
-      </c>
-      <c r="C63" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="B63" s="2" t="n">
         <v>45250</v>
       </c>
-      <c r="D63" t="n">
+      <c r="C63" t="n">
         <v>2</v>
       </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>(2200.0, 2300.0)</t>
+        </is>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>(2200.0, 2300.0)</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
           <t>Channel.C_006</t>
         </is>
       </c>
-      <c r="G63" t="n">
+      <c r="F63" t="n">
         <v>0.00479018499791497</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>2023-11-20_2_Channel.C_006</t>
+        </is>
+      </c>
+      <c r="H63" t="n">
+        <v>2200</v>
+      </c>
+      <c r="I63" t="n">
+        <v>2300</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>38</v>
-      </c>
-      <c r="B64" t="n">
-        <v>38</v>
-      </c>
-      <c r="C64" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="B64" s="2" t="n">
         <v>45255</v>
       </c>
-      <c r="D64" t="n">
+      <c r="C64" t="n">
         <v>1</v>
       </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>(1500.0, 1600.0)</t>
+        </is>
+      </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>(1500.0, 1600.0)</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
           <t>Channel.C_014</t>
         </is>
       </c>
-      <c r="G64" t="n">
+      <c r="F64" t="n">
         <v>0.0156939900887875</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>2023-11-25_1_Channel.C_014</t>
+        </is>
+      </c>
+      <c r="H64" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I64" t="n">
+        <v>1600</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>39</v>
-      </c>
-      <c r="B65" t="n">
-        <v>39</v>
-      </c>
-      <c r="C65" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="B65" s="2" t="n">
         <v>45255</v>
       </c>
-      <c r="D65" t="n">
+      <c r="C65" t="n">
         <v>1</v>
       </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>(100.0, 500.0)</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>(100.0, 500.0)</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
           <t>Channel.C_019</t>
         </is>
       </c>
-      <c r="G65" t="n">
+      <c r="F65" t="n">
         <v>0.0307663890018702</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>2023-11-25_1_Channel.C_019</t>
+        </is>
+      </c>
+      <c r="H65" t="n">
+        <v>100</v>
+      </c>
+      <c r="I65" t="n">
+        <v>500</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>40</v>
-      </c>
-      <c r="B66" t="n">
-        <v>40</v>
-      </c>
-      <c r="C66" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="B66" s="2" t="n">
         <v>45255</v>
       </c>
-      <c r="D66" t="n">
+      <c r="C66" t="n">
         <v>3</v>
       </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>(50.0, 150.0)</t>
+        </is>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>(50.0, 150.0)</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
           <t>Channel.C_018</t>
         </is>
       </c>
-      <c r="G66" t="n">
+      <c r="F66" t="n">
         <v>0.0363170926256485</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>2023-11-25_3_Channel.C_018</t>
+        </is>
+      </c>
+      <c r="H66" t="n">
+        <v>50</v>
+      </c>
+      <c r="I66" t="n">
+        <v>150</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>41</v>
-      </c>
-      <c r="B67" t="n">
-        <v>41</v>
-      </c>
-      <c r="C67" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="B67" s="2" t="n">
         <v>45258</v>
       </c>
-      <c r="D67" t="n">
+      <c r="C67" t="n">
         <v>3</v>
       </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>(700.0, 850.0)</t>
+        </is>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>(700.0, 850.0)</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
           <t>Channel.C_007</t>
         </is>
       </c>
-      <c r="G67" t="n">
+      <c r="F67" t="n">
         <v>0.0185877355832485</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>2023-11-28_3_Channel.C_007</t>
+        </is>
+      </c>
+      <c r="H67" t="n">
+        <v>700</v>
+      </c>
+      <c r="I67" t="n">
+        <v>850</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>42</v>
-      </c>
-      <c r="B68" t="n">
-        <v>42</v>
-      </c>
-      <c r="C68" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="B68" s="2" t="n">
         <v>45258</v>
       </c>
-      <c r="D68" t="n">
+      <c r="C68" t="n">
         <v>4</v>
       </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>(350.0, 500.0)</t>
+        </is>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>(350.0, 500.0)</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
           <t>Channel.C_015</t>
         </is>
       </c>
-      <c r="G68" t="n">
+      <c r="F68" t="n">
         <v>0.0341434537209639</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>2023-11-28_4_Channel.C_015</t>
+        </is>
+      </c>
+      <c r="H68" t="n">
+        <v>350</v>
+      </c>
+      <c r="I68" t="n">
+        <v>500</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>43</v>
-      </c>
-      <c r="B69" t="n">
-        <v>43</v>
-      </c>
-      <c r="C69" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="B69" s="2" t="n">
         <v>45265</v>
       </c>
-      <c r="D69" t="n">
+      <c r="C69" t="n">
         <v>4</v>
       </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>(650.0, 750.0)</t>
+        </is>
+      </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>(650.0, 750.0)</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
           <t>Channel.C_015</t>
         </is>
       </c>
-      <c r="G69" t="n">
+      <c r="F69" t="n">
         <v>0.0420897306933529</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>2023-12-05_4_Channel.C_015</t>
+        </is>
+      </c>
+      <c r="H69" t="n">
+        <v>650</v>
+      </c>
+      <c r="I69" t="n">
+        <v>750</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>44</v>
-      </c>
-      <c r="B70" t="n">
-        <v>44</v>
-      </c>
-      <c r="C70" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="B70" s="2" t="n">
         <v>45274</v>
       </c>
-      <c r="D70" t="n">
+      <c r="C70" t="n">
         <v>1</v>
       </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>(900.0, 1050.0)</t>
+        </is>
+      </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>(900.0, 1050.0)</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
           <t>Channel.C_008</t>
         </is>
       </c>
-      <c r="G70" t="n">
+      <c r="F70" t="n">
         <v>0.0387635591675108</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>2023-12-14_1_Channel.C_008</t>
+        </is>
+      </c>
+      <c r="H70" t="n">
+        <v>900</v>
+      </c>
+      <c r="I70" t="n">
+        <v>1050</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>45</v>
-      </c>
-      <c r="B71" t="n">
-        <v>45</v>
-      </c>
-      <c r="C71" s="2" t="n">
+        <v>69</v>
+      </c>
+      <c r="B71" s="2" t="n">
         <v>45274</v>
       </c>
-      <c r="D71" t="n">
+      <c r="C71" t="n">
         <v>1</v>
       </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>(1450.0, 1750.0)</t>
+        </is>
+      </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>(1450.0, 1750.0)</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
           <t>Channel.C_024</t>
         </is>
       </c>
-      <c r="G71" t="n">
+      <c r="F71" t="n">
         <v>2.86335363152876e-05</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>2023-12-14_1_Channel.C_024</t>
+        </is>
+      </c>
+      <c r="H71" t="n">
+        <v>1450</v>
+      </c>
+      <c r="I71" t="n">
+        <v>1750</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46</v>
-      </c>
-      <c r="B72" t="n">
-        <v>46</v>
-      </c>
-      <c r="C72" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="B72" s="2" t="n">
         <v>45274</v>
       </c>
-      <c r="D72" t="n">
+      <c r="C72" t="n">
         <v>4</v>
       </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>(1900.0, 2000.0)</t>
+        </is>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>(1900.0, 2000.0)</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
           <t>Channel.C_006</t>
         </is>
       </c>
-      <c r="G72" t="n">
+      <c r="F72" t="n">
         <v>0.0148327445015081</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>2023-12-14_4_Channel.C_006</t>
+        </is>
+      </c>
+      <c r="H72" t="n">
+        <v>1900</v>
+      </c>
+      <c r="I72" t="n">
+        <v>2000</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>47</v>
-      </c>
-      <c r="B73" t="n">
-        <v>47</v>
-      </c>
-      <c r="C73" s="2" t="n">
+        <v>71</v>
+      </c>
+      <c r="B73" s="2" t="n">
         <v>45274</v>
       </c>
-      <c r="D73" t="n">
+      <c r="C73" t="n">
         <v>4</v>
       </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>(750.0, 850.0)</t>
+        </is>
+      </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>(750.0, 850.0)</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
           <t>Channel.C_008</t>
         </is>
       </c>
-      <c r="G73" t="n">
+      <c r="F73" t="n">
         <v>0.0423018416670973</v>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>2023-12-14_4_Channel.C_008</t>
+        </is>
+      </c>
+      <c r="H73" t="n">
+        <v>750</v>
+      </c>
+      <c r="I73" t="n">
+        <v>850</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>48</v>
-      </c>
-      <c r="B74" t="n">
-        <v>48</v>
-      </c>
-      <c r="C74" s="2" t="n">
+        <v>72</v>
+      </c>
+      <c r="B74" s="2" t="n">
         <v>45278</v>
       </c>
-      <c r="D74" t="n">
+      <c r="C74" t="n">
         <v>2</v>
       </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>(200.0, 350.0)</t>
+        </is>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>(200.0, 350.0)</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
           <t>Channel.C_012_Unit 2</t>
         </is>
       </c>
-      <c r="G74" t="n">
+      <c r="F74" t="n">
         <v>0.0379316883083251</v>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>2023-12-18_2_Channel.C_012_Unit 2</t>
+        </is>
+      </c>
+      <c r="H74" t="n">
+        <v>200</v>
+      </c>
+      <c r="I74" t="n">
+        <v>350</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>49</v>
-      </c>
-      <c r="B75" t="n">
-        <v>49</v>
-      </c>
-      <c r="C75" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B75" s="2" t="n">
         <v>45278</v>
       </c>
-      <c r="D75" t="n">
+      <c r="C75" t="n">
         <v>3</v>
       </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>(2000.0, 2150.0)</t>
+        </is>
+      </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>(2000.0, 2150.0)</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
           <t>Channel.C_015_Unit 1</t>
         </is>
       </c>
-      <c r="G75" t="n">
+      <c r="F75" t="n">
         <v>0.0374272936245397</v>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>2023-12-18_3_Channel.C_015_Unit 1</t>
+        </is>
+      </c>
+      <c r="H75" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I75" t="n">
+        <v>2150</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="B76" t="n">
-        <v>50</v>
-      </c>
-      <c r="C76" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="B76" s="2" t="n">
         <v>45278</v>
       </c>
-      <c r="D76" t="n">
+      <c r="C76" t="n">
         <v>3</v>
       </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>(150.0, 400.0)</t>
+        </is>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>(150.0, 400.0)</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
           <t>Channel.C_020_Unit 1</t>
         </is>
       </c>
-      <c r="G76" t="n">
+      <c r="F76" t="n">
         <v>0.0108022991106536</v>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>2023-12-18_3_Channel.C_020_Unit 1</t>
+        </is>
+      </c>
+      <c r="H76" t="n">
+        <v>150</v>
+      </c>
+      <c r="I76" t="n">
+        <v>400</v>
       </c>
     </row>
   </sheetData>
